--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487622_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487622_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4754</v>
+        <v>5.1754</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4907</v>
+        <v>4.5723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9847</v>
+        <v>0.6031</v>
       </c>
       <c r="G2" t="n">
         <v>2.1309</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2968</v>
+        <v>0.9968</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8835</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4949</v>
+        <v>0.1133</v>
       </c>
       <c r="V2" t="n">
         <v>1.2716</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3244</v>
+        <v>4.2224</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8312</v>
+        <v>3.1276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4932</v>
+        <v>1.0948</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9696</v>
+        <v>0.1339</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8529</v>
+        <v>-1.4088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1168</v>
+        <v>1.5427</v>
       </c>
       <c r="J3" t="n">
-        <v>1.899</v>
+        <v>1.0373</v>
       </c>
       <c r="K3" t="n">
-        <v>1.899</v>
+        <v>-0.9392</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.9765</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0706</v>
+        <v>-0.9034</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0462</v>
+        <v>-0.4696</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1168</v>
+        <v>-0.4338</v>
       </c>
       <c r="P3" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2189</v>
+        <v>0.2423</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3963</v>
+        <v>0.4262</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1774</v>
+        <v>-0.1839</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9418</v>
+        <v>2.6821</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>2.6343</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5642</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1469</v>
+        <v>4.0793</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3021</v>
+        <v>2.1583</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8448</v>
+        <v>1.921</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7927999999999999</v>
+        <v>2.5736</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2884</v>
+        <v>1.7449</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5044</v>
+        <v>0.8286</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4574</v>
+        <v>2.358</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0247</v>
+        <v>1.1122</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4821</v>
+        <v>1.2458</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3354</v>
+        <v>0.2156</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3131</v>
+        <v>0.6327</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0223</v>
+        <v>-0.4171</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>2.074</v>
+        <v>0.5818</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2999</v>
+        <v>0.4287</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7741</v>
+        <v>0.1531</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0597</v>
+        <v>1.506</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4</v>
+        <v>1.506</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7702</v>
+        <v>3.5964</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8765</v>
+        <v>3.1305</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8937</v>
+        <v>0.466</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5736</v>
+        <v>1.9696</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7449</v>
+        <v>1.8529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8286</v>
+        <v>0.1168</v>
       </c>
       <c r="J5" t="n">
-        <v>2.358</v>
+        <v>1.899</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1122</v>
+        <v>1.899</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2458</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2156</v>
+        <v>0.0706</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6327</v>
+        <v>-0.0462</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4171</v>
+        <v>0.1168</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2728</v>
+        <v>0.491</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1469</v>
+        <v>0.6956</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1259</v>
+        <v>-0.2047</v>
       </c>
       <c r="V5" t="n">
-        <v>1.506</v>
+        <v>0.9418</v>
       </c>
       <c r="W5" t="n">
         <v>1.506</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3132</v>
+        <v>3.3582</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5455</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7677</v>
+        <v>2.7358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1339</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4088</v>
+        <v>-0.2884</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5427</v>
+        <v>-0.5044</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0373</v>
+        <v>-0.4574</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9392</v>
+        <v>0.0247</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9765</v>
+        <v>-0.4821</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9034</v>
+        <v>-0.3354</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4696</v>
+        <v>-0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4338</v>
+        <v>-0.0223</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6669</v>
+        <v>1.2853</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1559</v>
+        <v>0.6202</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.511</v>
+        <v>0.6651</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6821</v>
+        <v>3.0597</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6343</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0478</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3931</v>
+        <v>3.2572</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3191</v>
+        <v>3.1014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.074</v>
+        <v>0.1558</v>
       </c>
       <c r="G7" t="n">
         <v>0.9132</v>
@@ -1000,13 +1000,13 @@
         <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4917</v>
+        <v>0.3724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8233</v>
+        <v>-0.041</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3316</v>
+        <v>0.4133</v>
       </c>
       <c r="V7" t="n">
         <v>2.1657</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6339</v>
+        <v>1.2246</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3828</v>
+        <v>3.0825</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7489</v>
+        <v>-1.8579</v>
       </c>
       <c r="G8" t="n">
         <v>0.3631</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8246</v>
+        <v>0.4153</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7896</v>
+        <v>0.4893</v>
       </c>
       <c r="U8" t="n">
-        <v>0.035</v>
+        <v>-0.074</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3299</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.58</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1443</v>
+        <v>0.0164</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7242</v>
+        <v>0.588</v>
       </c>
       <c r="G9" t="n">
         <v>0.6037</v>
@@ -1156,13 +1156,13 @@
         <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>1.024</v>
+        <v>1.0484</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5709</v>
+        <v>0.7315</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4531</v>
+        <v>0.3169</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6597</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2337</v>
+        <v>-0.2065</v>
       </c>
       <c r="E10" t="n">
         <v>0.0206</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2543</v>
+        <v>-0.2271</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2519</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2247</v>
+        <v>-1.515</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.305</v>
+        <v>-1.7044</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0803</v>
+        <v>0.1893</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6977</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.109</v>
+        <v>0.6006</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0852</v>
+        <v>0.6858</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8848</v>
+        <v>-2.594</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4256</v>
+        <v>-3.3255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7316</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9435</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3697</v>
+        <v>-0.0788</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0965</v>
+        <v>0.0036</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2732</v>
+        <v>-0.0824</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3776</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.2939</v>
+        <v>21.2023</v>
       </c>
       <c r="E13" t="n">
-        <v>13.8936</v>
+        <v>14.8022</v>
       </c>
       <c r="F13" t="n">
-        <v>6.400200000000001</v>
+        <v>6.4004</v>
       </c>
       <c r="G13" t="n">
         <v>3.0021</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6395</v>
+        <v>1.639499999999999</v>
       </c>
       <c r="I13" t="n">
         <v>1.3626</v>
       </c>
       <c r="J13" t="n">
-        <v>6.632500000000001</v>
+        <v>6.632499999999998</v>
       </c>
       <c r="K13" t="n">
         <v>2.4057</v>
@@ -1468,10 +1468,10 @@
         <v>14.5524</v>
       </c>
       <c r="S13" t="n">
-        <v>5.092000000000001</v>
+        <v>6.000500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.015000000000001</v>
+        <v>4.9234</v>
       </c>
       <c r="U13" t="n">
         <v>1.0769</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.265</v>
+        <v>2.1957</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5084</v>
+        <v>4.3725</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7566000000000001</v>
+        <v>-2.1769</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.722</v>
+        <v>0.8956</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1706</v>
+        <v>1.7598</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8925999999999999</v>
+        <v>-0.8642</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8086</v>
+        <v>2.3994</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6056</v>
+        <v>2.2904</v>
       </c>
       <c r="L14" t="n">
-        <v>0.203</v>
+        <v>0.109</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5306</v>
+        <v>-1.5038</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.435</v>
+        <v>-0.5306</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0956</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P14" t="n">
         <v>0.7761</v>
@@ -1546,28 +1546,28 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7586</v>
+        <v>-0.8701</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1058</v>
+        <v>-0.1164</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6528</v>
+        <v>-0.7537</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4522</v>
+        <v>1.394</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5642</v>
+        <v>3.0597</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1119</v>
+        <v>-1.6656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0523</v>
+        <v>0.9191</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4717</v>
+        <v>0.7076</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4194</v>
+        <v>0.2115</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8956</v>
+        <v>-0.722</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7598</v>
+        <v>0.1706</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8642</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3994</v>
+        <v>0.8086</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2904</v>
+        <v>0.6056</v>
       </c>
       <c r="L15" t="n">
-        <v>0.109</v>
+        <v>0.203</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5038</v>
+        <v>-1.5306</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5306</v>
+        <v>-0.435</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-1.0956</v>
       </c>
       <c r="P15" t="n">
         <v>0.7761</v>
@@ -1624,22 +1624,22 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0134</v>
+        <v>0.4127</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0173</v>
+        <v>0.305</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9961</v>
+        <v>0.1077</v>
       </c>
       <c r="V15" t="n">
-        <v>1.394</v>
+        <v>0.4522</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0597</v>
+        <v>0.5642</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6656</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4498</v>
+        <v>-0.0569</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5257</v>
+        <v>3.7249</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.076</v>
+        <v>-3.7818</v>
       </c>
       <c r="G16" t="n">
         <v>1.0991</v>
@@ -1702,13 +1702,13 @@
         <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1389</v>
+        <v>-0.6455</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9847</v>
+        <v>0.1839</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1236</v>
+        <v>-0.8294</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1224</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9909</v>
+        <v>-2.1211</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3411</v>
+        <v>-1.7694</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3321</v>
+        <v>-0.3518</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2098</v>
+        <v>-1.3621</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5998</v>
+        <v>-3.0499</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8096</v>
+        <v>1.6878</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3225</v>
+        <v>-0.3862</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0412</v>
+        <v>-2.2409</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2813</v>
+        <v>1.8547</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1127</v>
+        <v>-0.9759</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.641</v>
+        <v>-0.8091</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5283</v>
+        <v>-0.1669</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0247</v>
+        <v>-0.7635</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1828</v>
+        <v>-0.219</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2075</v>
+        <v>-0.5445</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4</v>
+        <v>-0.7716</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4</v>
+        <v>-0.7716</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3059</v>
+        <v>-2.2301</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4566</v>
+        <v>0.241</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7625</v>
+        <v>-2.4711</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8994</v>
+        <v>1.2098</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3889</v>
+        <v>-0.5998</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5105</v>
+        <v>1.8096</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6495</v>
+        <v>1.3225</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6495</v>
+        <v>1.2813</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2498</v>
+        <v>-0.1127</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3889</v>
+        <v>-0.641</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.139</v>
+        <v>0.5283</v>
       </c>
       <c r="P18" t="n">
-        <v>0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R18" t="n">
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3874</v>
+        <v>-0.2638</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0011</v>
+        <v>0.0827</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3885</v>
+        <v>-0.3465</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.0119</v>
+        <v>-2.4</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.0119</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4111</v>
+        <v>-2.2532</v>
       </c>
       <c r="E19" t="n">
         <v>-3.0421</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6311</v>
+        <v>0.789</v>
       </c>
       <c r="G19" t="n">
         <v>0.0138</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2308</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5451</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3143</v>
+        <v>0.4722</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2239</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GIFREU LLARCH</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5006</v>
+        <v>-2.2547</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5994</v>
+        <v>0.1563</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9012</v>
+        <v>-2.411</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9749</v>
+        <v>0.8994</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7985</v>
+        <v>0.3889</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8236</v>
+        <v>0.5105</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2892</v>
+        <v>0.6495</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9516</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2407</v>
+        <v>0.6495</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2641</v>
+        <v>0.2498</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8469</v>
+        <v>0.3889</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4171</v>
+        <v>-0.139</v>
       </c>
       <c r="P20" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.3362</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.2992</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-3.0119</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.9702</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.3952</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.7413</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.3461</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.9209</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.6597</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.2612</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5709</v>
+        <v>-2.6986</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8705</v>
+        <v>-1.8436</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7004</v>
+        <v>-0.855</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3621</v>
+        <v>-0.1932</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.0499</v>
+        <v>-0.1821</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6878</v>
+        <v>-0.0111</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3862</v>
+        <v>-0.2925</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2409</v>
+        <v>-0.2925</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8547</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9759</v>
+        <v>0.0992</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8091</v>
+        <v>0.1104</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1669</v>
+        <v>-0.0111</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1642</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2133</v>
+        <v>0.1155</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3201</v>
+        <v>-0.387</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8932</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7716</v>
+        <v>-2.8149</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7716</v>
+        <v>-2.8149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>L. GIFREU LLARCH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6384</v>
+        <v>-2.7435</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.244</v>
+        <v>-1.3001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3944</v>
+        <v>-1.4435</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1932</v>
+        <v>-0.9749</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1821</v>
+        <v>-1.7985</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0111</v>
+        <v>0.8236</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2925</v>
+        <v>0.2892</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2925</v>
+        <v>-0.9516</v>
       </c>
       <c r="L22" t="n">
+        <v>1.2407</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.2641</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.8469</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.4171</v>
+      </c>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>0.0992</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.1104</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.0111</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.194</v>
-      </c>
       <c r="Q22" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8244</v>
+        <v>0.1522</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7874</v>
+        <v>0.0406</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.037</v>
+        <v>0.1116</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.8149</v>
+        <v>-1.9209</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8149</v>
+        <v>-1.2612</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.643</v>
+        <v>-7.0485</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.9478</v>
+        <v>-7.6475</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3048</v>
+        <v>0.599</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8673</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.413</v>
+        <v>-0.8185</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4229</v>
+        <v>-0.1226</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9901</v>
+        <v>-0.6959</v>
       </c>
       <c r="V23" t="n">
         <v>0.1597</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.2937</v>
+        <v>-18.2918</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.400300000000001</v>
+        <v>-6.400400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.8935</v>
+        <v>-11.8916</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0018</v>
@@ -2326,13 +2326,13 @@
         <v>12.6123</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.0921</v>
+        <v>-3.0901</v>
       </c>
       <c r="T24" t="n">
         <v>-1.0771</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.015</v>
+        <v>-2.013</v>
       </c>
       <c r="V24" t="n">
         <v>-10.2597</v>
